--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="115">
   <si>
     <t>Reference</t>
   </si>
@@ -31,9 +31,6 @@
     <t>Purchase-URL</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
     <t>C1</t>
   </si>
   <si>
@@ -43,7 +40,7 @@
     <t>Capacitor_SMD:C_0603_1608Metric</t>
   </si>
   <si>
-    <t>https://robu.in/product/4-7nf-4700pf-50v-capacitor-0603-smd-package-pack-of-30/</t>
+    <t>https://robu.in/product/gcm188r91h472ka37d-murata-electronics-50v-4-7nf-x8r-%c2%b110-0603-multilayer-ceramic-capacitors-mlcc-smd-smt-rohs/</t>
   </si>
   <si>
     <t>C3,C8</t>
@@ -55,7 +52,7 @@
     <t>Capacitor_SMD:C_0805_2012Metric</t>
   </si>
   <si>
-    <t>https://robu.in/product/1uf-1000nf-50v-capacitor-0805-smd-package-pack-of-10/</t>
+    <t>https://robu.in/product/cc0805kkx7r0bb105-yageo-100v-1uf-x7r-%c2%b110-0805-multilayer-ceramic-capacitors-mlcc-smd-smt-rohs/</t>
   </si>
   <si>
     <t>C4,C5</t>
@@ -64,10 +61,7 @@
     <t>4.7uF</t>
   </si>
   <si>
-    <t>https://robu.in/product/4-7uf-4700nf-50v-capacitor-0805-smd-package-pack-of-5/</t>
-  </si>
-  <si>
-    <t>Listed as pack of 5; Robu shows 9 as the price, check whether it is per piece or per pack at checkout</t>
+    <t>https://robu.in/product/0805x475k500nt-fh-50v-4-7uf-x5r%c2%b110-0805-multilayer-ceramic-capacitors-mlcc-smd-smt-rohs/</t>
   </si>
   <si>
     <t>C6,C7</t>
@@ -76,7 +70,7 @@
     <t>100nF</t>
   </si>
   <si>
-    <t>https://robu.in/product/100nf-0603-surface-mount-multilayer-ceramic-capacitor-pack-of-40/</t>
+    <t>https://robu.in/product/cc0603jrx7r7bb104-yageo-16v-100nf-x7r-%c2%b15-0603-multilayer-ceramic-capacitors-mlcc-smd-smt-rohs/</t>
   </si>
   <si>
     <t>C9,C10</t>
@@ -85,9 +79,6 @@
     <t>0.1uF</t>
   </si>
   <si>
-    <t>Same part as C6,C7 (0.1uF = 100nF)</t>
-  </si>
-  <si>
     <t>C11</t>
   </si>
   <si>
@@ -109,9 +100,6 @@
     <t>https://robu.in/product/1n4148-surface-mount-zener-diode-pack-of-30/</t>
   </si>
   <si>
-    <t>CHECK: BOM is 1N4148W-7-F (SOD-123 switching diode); Robu listing is titled a zener diode, confirm package/part before ordering</t>
-  </si>
-  <si>
     <t>D1</t>
   </si>
   <si>
@@ -166,9 +154,6 @@
     <t>https://robu.in/product/type-c-31-m-17-hroparts-1-6p-female-type-c-smd-usb-connectors-rohs/</t>
   </si>
   <si>
-    <t>CHECK: BOM footprint is TYPE-C-31-M-12, link is TYPE-C-31-M-17 (different variant)</t>
-  </si>
-  <si>
     <t>J2</t>
   </si>
   <si>
@@ -178,9 +163,6 @@
     <t>Connector_Wire:SolderWirePad_1x01_SMD_1x2mm</t>
   </si>
   <si>
-    <t>Solder pad on PCB, no part to buy (battery wire goes here)</t>
-  </si>
-  <si>
     <t>J3</t>
   </si>
   <si>
@@ -211,9 +193,6 @@
     <t>https://robu.in/product/rc0603jr-075k1l-yageo-res-thick-film-0603-5-1k-ohm-5-0-1w1-10w-%C2%B1100ppm-c-pad-smd-t-r/</t>
   </si>
   <si>
-    <t>Not in your link list; found on Robu</t>
-  </si>
-  <si>
     <t>R3</t>
   </si>
   <si>
@@ -256,18 +235,12 @@
     <t>https://robu.in/product/100-ohm-1-4w-0603-surface-mount-chip-resistor-pack-of-100/</t>
   </si>
   <si>
-    <t>Your 100ohm link was a ferrite bead (BLM18KG101, Rs 1.83), but BOM R11 is a 100 ohm 0603 resistor, so I used the resistor</t>
-  </si>
-  <si>
     <t>R12</t>
   </si>
   <si>
     <t>https://robu.in/product/ac0402jr-0750rl-yageo-res-thick-film-0402-50-ohm-5-0-063w1-16w-%c2%b1100ppm-c-pad-smd-t-r-automotive-aec-q200/</t>
   </si>
   <si>
-    <t>CHECK: link is 0402 but BOM footprint is 0603 (will not fit the pads). 51 ohm 0603 is the usual stock value</t>
-  </si>
-  <si>
     <t>R13,R14,R15</t>
   </si>
   <si>
@@ -301,9 +274,6 @@
     <t>https://robu.in/product/pts526-spg15-smtr2-lfs-ck-5-2mm-1-5mm-5-2mm-320gf-smd-tactile-switches-rohs/</t>
   </si>
   <si>
-    <t>CHECK: BOM is PTS526 SMG15, link is PTS526 SPG15 (actuator/variant differs)</t>
-  </si>
-  <si>
     <t>U2</t>
   </si>
   <si>
@@ -316,9 +286,6 @@
     <t>https://robu.in/product/espressif-esp32-c3-mini-1-h4-module/</t>
   </si>
   <si>
-    <t>CHECK: BOM is ESP32-C3-MINI-1U-H4 (external antenna, U.FL); link is MINI-1-H4 (PCB antenna). Different footprint</t>
-  </si>
-  <si>
     <t>U3</t>
   </si>
   <si>
@@ -343,9 +310,6 @@
     <t>https://robu.in/product/mcp73831t-2aci-ot-4-2v-500ma-single-cell-li-ion-li-polymer-battery-charge-management-controller-5-pin-sot-23-microchip-technology/</t>
   </si>
   <si>
-    <t>MCP73831T-2ACI/OT</t>
-  </si>
-  <si>
     <t>U5</t>
   </si>
   <si>
@@ -370,9 +334,6 @@
     <t>https://robu.in/product/usblc6-2sc6-stmicroelectronics-usblc6-2sc6-esd-protection-device-17-v-sot-23-6-pins-usblc/</t>
   </si>
   <si>
-    <t>CHECK: BOM is USBLC6-2P6 (SOT-666); link is USBLC6-2SC6 (SOT-23-6). Different package</t>
-  </si>
-  <si>
     <t>BT1</t>
   </si>
   <si>
@@ -383,9 +344,6 @@
   </si>
   <si>
     <t>https://robu.in/product/450mah-pcm-protected-micro-li-po-battery/</t>
-  </si>
-  <si>
-    <t>Added from your link list; not in the original BOM</t>
   </si>
   <si>
     <t>Y1</t>
@@ -404,7 +362,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -415,6 +373,10 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
     </font>
     <font>
       <u/>
@@ -435,7 +397,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -443,6 +405,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
@@ -686,428 +651,398 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1">
+        <v>3.59</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0.54</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1">
         <v>2.0</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1">
+        <v>4.97</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="E3" s="1">
-        <v>2.09</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1">
         <v>2.0</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1.89</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1">
         <v>2.0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" s="1">
-        <v>0.3</v>
+        <v>4.2</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" s="1">
         <v>2.0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1">
         <v>0.3</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B7" s="1">
         <v>1.0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" s="1">
         <v>1.14</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>27</v>
+      <c r="F7" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B8" s="1">
         <v>1.0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E8" s="1">
         <v>2.22</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>32</v>
+      <c r="F8" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1">
         <v>1.0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E9" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>36</v>
+        <v>1.52</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B10" s="1">
         <v>1.0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E10" s="1">
         <v>0.97</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>39</v>
+      <c r="F10" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B11" s="1">
         <v>1.0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E11" s="1">
         <v>1.91</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>42</v>
+      <c r="F11" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B12" s="1">
         <v>1.0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E12" s="1">
         <v>14.0</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>46</v>
+      <c r="F12" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B13" s="1">
         <v>1.0</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E13" s="1">
         <v>30.0</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>51</v>
+      <c r="F13" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B14" s="1">
         <v>1.0</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B15" s="1">
         <v>1.0</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B16" s="1">
         <v>1.0</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E16" s="1">
         <v>8.0</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>61</v>
+      <c r="F16" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B17" s="1">
         <v>2.0</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E17" s="1">
         <v>0.2</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>66</v>
+      <c r="F17" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B18" s="1">
         <v>1.0</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E18" s="1">
         <v>1.34</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>66</v>
+      <c r="F18" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B19" s="1">
         <v>3.0</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E19" s="1">
         <v>0.35</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>72</v>
+      <c r="F19" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B20" s="1">
         <v>1.0</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E20" s="1">
         <v>2.31</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>75</v>
+      <c r="F20" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B21" s="1">
         <v>3.0</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E21" s="1">
         <v>0.86</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>66</v>
+      <c r="F21" s="3" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B22" s="1">
         <v>1.0</v>
@@ -1116,21 +1051,18 @@
         <v>100.0</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E22" s="1">
         <v>0.86</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>81</v>
+      <c r="F22" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B23" s="1">
         <v>1.0</v>
@@ -1139,246 +1071,222 @@
         <v>50.0</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E23" s="1">
         <v>0.68</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>84</v>
+      <c r="F23" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="B24" s="1">
         <v>3.0</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E24" s="1">
         <v>0.45</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>66</v>
+      <c r="F24" s="3" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B25" s="1">
         <v>1.0</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E25" s="1">
         <v>37.0</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>91</v>
+      <c r="F25" s="3" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B26" s="1">
         <v>1.0</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E26" s="1">
         <v>13.0</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>96</v>
+      <c r="F26" s="3" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B27" s="1">
         <v>1.0</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E27" s="1">
         <v>249.0</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>101</v>
+      <c r="F27" s="3" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B28" s="1">
         <v>1.0</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="E28" s="1">
         <v>569.0</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>105</v>
+      <c r="F28" s="3" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B29" s="1">
         <v>1.0</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="E29" s="1">
         <v>139.0</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>110</v>
+      <c r="F29" s="3" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="B30" s="1">
         <v>1.0</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="E30" s="1">
         <v>22.0</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>114</v>
+      <c r="F30" s="3" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="B31" s="1">
         <v>1.0</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E31" s="1">
         <v>14.0</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>119</v>
+      <c r="F31" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="B32" s="1">
         <v>1.0</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="E32" s="1">
         <v>299.0</v>
       </c>
-      <c r="F32" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>124</v>
+      <c r="F32" s="3" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="B33" s="1">
         <v>1.0</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="E33" s="1">
-        <v>96.0</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>124</v>
+        <v>41.0</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E34" s="3">
+        <v>114</v>
+      </c>
+      <c r="E34" s="4">
         <f>SUM(E2:E33)</f>
-        <v>1517.29</v>
+        <v>1464.76</v>
       </c>
     </row>
   </sheetData>
